--- a/Assignments/Assignment I.xlsx
+++ b/Assignments/Assignment I.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashok\OneDrive\Desktop\Cloud Computing\cloudcomputing\Assignments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5D7FE2-38D0-4E46-97C0-FC12C80953B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF1C936-4798-4826-948A-5FF9F6D91BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{A4797BCA-401C-43AC-AE7D-E84C4E10D569}"/>
   </bookViews>
@@ -541,7 +541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -549,7 +549,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -557,7 +557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
